--- a/src/Tests/Tests.AbsPath.Net.verified.xlsx
+++ b/src/Tests/Tests.AbsPath.Net.verified.xlsx
@@ -7,8 +7,8 @@
     <workbookView xWindow="4290" yWindow="4290" windowWidth="38700" windowHeight="15345" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
-    <sheet name="Evaluation Warning" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="DeterministicId5"/>
+    <sheet name="Evaluation Warning" sheetId="2" r:id="DeterministicId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029"/>
